--- a/Versão5/GASE/Ontologia_Gases.xlsx
+++ b/Versão5/GASE/Ontologia_Gases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8970F1-48E6-4D85-BE2F-997FA66FFFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232CD4FE-6666-41B3-8700-696DCC2C68CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Interop" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!$C$2:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Classes!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="260">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -327,16 +327,7 @@
     <t>Contêiner</t>
   </si>
   <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>Produzido</t>
-  </si>
-  <si>
     <t>Informação</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informção de acordo à norma NBR 19650-1.</t>
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
@@ -383,9 +374,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard.</t>
-  </si>
-  <si>
     <t>CTI_Projeto_01</t>
   </si>
   <si>
@@ -825,6 +813,45 @@
   </si>
   <si>
     <t>[ OST_PipeAccessory ]</t>
+  </si>
+  <si>
+    <t>Definida</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Requerida</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>No.Projeto</t>
+  </si>
+  <si>
+    <t>Requisito.Espacial</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Mobiliário</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Equipamento</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Sistemas</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
 </sst>
 </file>
@@ -932,12 +959,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2AA84"/>
         <bgColor rgb="FFF6C6AD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E896"/>
-        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1052,6 +1073,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1169,22 +1196,22 @@
   </cellStyleXfs>
   <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1200,10 +1227,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1215,64 +1242,61 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1281,7 +1305,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1296,7 +1320,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1308,7 +1332,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1326,29 +1350,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1359,20 +1380,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1489,6 +1522,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1516,6 +1557,44 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1960,10 +2039,10 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="40.07421875" style="64" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="64"/>
+    <col min="1" max="1" width="8.69140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="40.07421875" style="62" customWidth="1"/>
+    <col min="3" max="3" width="3.4609375" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1973,8 +2052,8 @@
       <c r="B1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="44" t="s">
-        <v>96</v>
+      <c r="C1" s="43" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1984,8 +2063,8 @@
       <c r="B2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="45" t="s">
-        <v>97</v>
+      <c r="C2" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -1993,10 +2072,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>97</v>
+        <v>123</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2006,8 +2085,8 @@
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>97</v>
+      <c r="C4" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2018,8 +2097,8 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>97</v>
+      <c r="C5" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2030,8 +2109,8 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>97</v>
+      <c r="C6" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2041,19 +2120,19 @@
       <c r="B7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="42" t="s">
+      <c r="C7" s="44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="44" t="s">
         <v>94</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2063,8 +2142,8 @@
       <c r="B9" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>97</v>
+      <c r="C9" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2074,8 +2153,8 @@
       <c r="B10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>97</v>
+      <c r="C10" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2085,8 +2164,8 @@
       <c r="B11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="45" t="s">
-        <v>97</v>
+      <c r="C11" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2096,8 +2175,8 @@
       <c r="B12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>97</v>
+      <c r="C12" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2107,8 +2186,8 @@
       <c r="B13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="45" t="s">
-        <v>97</v>
+      <c r="C13" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2118,8 +2197,8 @@
       <c r="B14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>97</v>
+      <c r="C14" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2129,8 +2208,8 @@
       <c r="B15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="45" t="s">
-        <v>97</v>
+      <c r="C15" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2140,8 +2219,8 @@
       <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>97</v>
+      <c r="C16" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2149,10 +2228,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>97</v>
+        <v>124</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2161,10 +2240,10 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46135.36063865741</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>97</v>
+        <v>46139.495710648145</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2174,8 +2253,8 @@
       <c r="B19" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="45" t="s">
-        <v>97</v>
+      <c r="C19" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2185,8 +2264,8 @@
       <c r="B20" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="45" t="s">
-        <v>97</v>
+      <c r="C20" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2196,8 +2275,8 @@
       <c r="B21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="45" t="s">
-        <v>97</v>
+      <c r="C21" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2205,10 +2284,10 @@
         <v>72</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>97</v>
+        <v>125</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2216,22 +2295,22 @@
         <v>73</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="43" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Household and Hospital Gas Objects</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>99</v>
+      <c r="C24" s="44" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2242,7 +2321,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.3046875" customWidth="1"/>
@@ -2250,8 +2329,8 @@
     <col min="3" max="3" width="7.765625" customWidth="1"/>
     <col min="4" max="4" width="9.07421875" customWidth="1"/>
     <col min="5" max="5" width="11.53515625" customWidth="1"/>
-    <col min="6" max="6" width="11.765625" style="47" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="37" customWidth="1"/>
+    <col min="6" max="6" width="11.765625" style="46" customWidth="1"/>
+    <col min="7" max="11" width="6.3046875" style="36" customWidth="1"/>
     <col min="12" max="12" width="7.4609375" customWidth="1"/>
     <col min="13" max="13" width="5.3046875" customWidth="1"/>
     <col min="14" max="14" width="10.921875" customWidth="1"/>
@@ -2263,94 +2342,94 @@
     <col min="20" max="20" width="7.23046875" customWidth="1"/>
     <col min="21" max="21" width="10.84375" customWidth="1"/>
     <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="62" customWidth="1"/>
-    <col min="24" max="24" width="53" style="62" customWidth="1"/>
-    <col min="25" max="25" width="18.23046875" style="63" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="37" customWidth="1"/>
-    <col min="27" max="27" width="31.765625" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" style="67" customWidth="1"/>
+    <col min="24" max="24" width="53" style="60" customWidth="1"/>
+    <col min="25" max="25" width="18.23046875" style="61" customWidth="1"/>
+    <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
+    <col min="27" max="27" width="40.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="50" t="s">
+      <c r="A1" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="40" t="s">
+      <c r="L1" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="P1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="S1" s="40" t="s">
+      <c r="R1" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="S1" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="T1" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="53" t="s">
+      <c r="U1" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="V1" s="39" t="s">
         <v>34</v>
       </c>
       <c r="W1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="40" t="s">
+      <c r="X1" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z1" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA1" s="40" t="s">
         <v>90</v>
-      </c>
-      <c r="Y1" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z1" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" s="41" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2358,77 +2437,77 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="33" t="str">
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="M2" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N2" s="33" t="str">
+        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Definida</v>
+      </c>
+      <c r="O2" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>No Projeto</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q2" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="34" t="str">
-        <f t="shared" ref="L2:L21" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="34" t="str">
-        <f t="shared" ref="M2:M21" si="1">CONCATENATE("", D2)</f>
-        <v>Produzido</v>
-      </c>
-      <c r="N2" s="34" t="str">
-        <f t="shared" ref="N2:N21" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+      <c r="R2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="35" t="str">
+        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="T2" s="35" t="str">
+        <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="O2" s="30" t="str">
-        <f t="shared" ref="O2:O10" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="36" t="str">
-        <f t="shared" ref="T2" si="4">SUBSTITUTE(D2, "_", " ")</f>
-        <v>Produzido</v>
-      </c>
-      <c r="U2" s="36" t="str">
-        <f t="shared" ref="U2:U21" si="5">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Informação</v>
-      </c>
-      <c r="V2" s="36" t="str">
-        <f t="shared" ref="V2" si="6">SUBSTITUTE(C2, "_", " ")</f>
-        <v>Gestão</v>
+      <c r="U2" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Definida</v>
+      </c>
+      <c r="V2" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W2" s="66" t="str">
-        <f>CONCATENATE("Key-GAS-",A2)</f>
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
       <c r="X2" s="30" t="s">
@@ -2437,11 +2516,12 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="30" t="s">
-        <v>103</v>
+      <c r="Z2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="30" t="str">
+        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2449,88 +2529,91 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="34" t="str">
+        <v>250</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M3" s="34" t="str">
+        <v>Contêiner</v>
+      </c>
+      <c r="M3" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N3" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N3" s="34" t="str">
+        <v>Requerida</v>
+      </c>
+      <c r="O3" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Espacial</v>
+      </c>
+      <c r="P3" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>Sistema de Gás</v>
-      </c>
-      <c r="O3" s="30" t="str">
+        <v>Contêiner</v>
+      </c>
+      <c r="T3" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U3" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V3" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W3" s="66" t="str">
         <f t="shared" si="3"/>
-        <v>Sistema.GAS</v>
-      </c>
-      <c r="P3" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q3" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T3" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="36" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.de.Gás</v>
-      </c>
-      <c r="V3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W3" s="66" t="str">
-        <f t="shared" ref="W3:W25" si="7">CONCATENATE("Key-GAS-",A3)</f>
         <v>Key-GAS-3</v>
       </c>
-      <c r="X3" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z3" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="AA3" s="30" t="s">
-        <v>219</v>
+      <c r="X3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2538,88 +2621,91 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F4" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="34" t="str">
-        <f t="shared" ref="L4:L15" si="8">CONCATENATE("", C4)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M4" s="34" t="str">
-        <f t="shared" ref="M4:M15" si="9">CONCATENATE("", D4)</f>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N4" s="34" t="str">
-        <f t="shared" ref="N4:N15" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O4" s="30" t="str">
+        <v>250</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M4" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N4" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O4" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Mobiliário</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U4" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V4" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W4" s="66" t="str">
         <f t="shared" si="3"/>
-        <v>Sistema.Oxigênio</v>
-      </c>
-      <c r="P4" s="59" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q4" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T4" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U4" s="36" t="str">
-        <f t="shared" ref="U4:U15" si="11">SUBSTITUTE(E4, "_", " ")</f>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W4" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-4</v>
       </c>
-      <c r="X4" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z4" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA4" s="30" t="s">
-        <v>220</v>
+      <c r="X4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2627,88 +2713,91 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F5" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="34" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M5" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N5" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O5" s="30" t="str">
+        <v>250</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M5" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N5" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O5" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Equipamento</v>
+      </c>
+      <c r="P5" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U5" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W5" s="66" t="str">
         <f t="shared" si="3"/>
-        <v>Sistema.Ar.Medicinal</v>
-      </c>
-      <c r="P5" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q5" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T5" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U5" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W5" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-5</v>
       </c>
-      <c r="X5" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y5" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z5" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>221</v>
+      <c r="X5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2716,88 +2805,91 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="67" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="34" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M6" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N6" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O6" s="30" t="str">
+        <v>250</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M6" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N6" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O6" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Sistemas</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U6" s="35" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V6" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W6" s="66" t="str">
         <f t="shared" si="3"/>
-        <v>Sistema.Ar.Comprimido</v>
-      </c>
-      <c r="P6" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q6" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="R6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T6" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U6" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V6" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W6" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-6</v>
       </c>
-      <c r="X6" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y6" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z6" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>222</v>
+      <c r="X6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2807,86 +2899,86 @@
       <c r="B7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F7" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="34" t="str">
-        <f t="shared" si="8"/>
+      <c r="C7" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="33" t="str">
+        <f t="shared" ref="L7:L25" si="5">CONCATENATE("", C7)</f>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M7" s="34" t="str">
-        <f t="shared" si="9"/>
+      <c r="M7" s="33" t="str">
+        <f t="shared" ref="M7:M25" si="6">CONCATENATE("", D7)</f>
         <v>Sistema.Gases</v>
       </c>
-      <c r="N7" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v>Sistema de Gás Hospitalar</v>
+      <c r="N7" s="33" t="str">
+        <f t="shared" ref="N7:N25" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <v>Sistema de Gás</v>
       </c>
       <c r="O7" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Óxido.Nitroso</v>
-      </c>
-      <c r="P7" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q7" s="59" t="s">
+        <f t="shared" ref="O7:O14" si="8">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
+        <v>Sistema.GAS</v>
+      </c>
+      <c r="P7" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q7" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U7" s="35" t="str">
+        <f t="shared" ref="U7:U25" si="9">SUBSTITUTE(E7, "_", " ")</f>
+        <v>Sistema.de.Gás</v>
+      </c>
+      <c r="V7" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W7" s="66" t="str">
+        <f t="shared" ref="W7:W30" si="10">CONCATENATE("Key-GAS-",A7)</f>
+        <v>Key-GAS-7</v>
+      </c>
+      <c r="X7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y7" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="R7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T7" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U7" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V7" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W7" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-7</v>
-      </c>
-      <c r="X7" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y7" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z7" s="35" t="s">
-        <v>249</v>
+      <c r="Z7" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2896,86 +2988,86 @@
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F8" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="34" t="str">
+      <c r="C8" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="33" t="str">
+        <f t="shared" ref="L8:L19" si="11">CONCATENATE("", C8)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M8" s="33" t="str">
+        <f t="shared" ref="M8:M19" si="12">CONCATENATE("", D8)</f>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N8" s="33" t="str">
+        <f t="shared" ref="N8:N19" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <v>Sistema de Gás Hospitalar</v>
+      </c>
+      <c r="O8" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M8" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N8" s="34" t="str">
+        <v>Sistema.Oxigênio</v>
+      </c>
+      <c r="P8" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q8" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T8" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U8" s="35" t="str">
+        <f t="shared" ref="U8:U19" si="14">SUBSTITUTE(E8, "_", " ")</f>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V8" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W8" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O8" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Nitrogênio</v>
-      </c>
-      <c r="P8" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q8" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T8" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U8" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V8" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W8" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z8" s="35" t="s">
-        <v>249</v>
+        <v>191</v>
+      </c>
+      <c r="Z8" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2985,86 +3077,86 @@
       <c r="B9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="67" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="34" t="str">
-        <f t="shared" ref="L9" si="12">CONCATENATE("", C9)</f>
+      <c r="C9" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M9" s="34" t="str">
-        <f t="shared" ref="M9" si="13">CONCATENATE("", D9)</f>
+      <c r="M9" s="33" t="str">
+        <f t="shared" si="12"/>
         <v>Sistema.Gases</v>
       </c>
-      <c r="N9" s="34" t="str">
-        <f t="shared" ref="N9" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
+      <c r="N9" s="33" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Hélio</v>
-      </c>
-      <c r="P9" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q9" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T9" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U9" s="36" t="str">
-        <f t="shared" ref="U9" si="15">SUBSTITUTE(E9, "_", " ")</f>
+        <f t="shared" si="8"/>
+        <v>Sistema.Ar.Medicinal</v>
+      </c>
+      <c r="P9" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q9" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T9" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U9" s="35" t="str">
+        <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
-      <c r="V9" s="36" t="s">
-        <v>118</v>
+      <c r="V9" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W9" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z9" s="35" t="s">
-        <v>249</v>
+        <v>191</v>
+      </c>
+      <c r="Z9" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3074,86 +3166,86 @@
       <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="34" t="str">
+      <c r="C10" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M10" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N10" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema de Gás Hospitalar</v>
+      </c>
+      <c r="O10" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M10" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N10" s="34" t="str">
+        <v>Sistema.Ar.Comprimido</v>
+      </c>
+      <c r="P10" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q10" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="R10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U10" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V10" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W10" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema de Gás Hospitalar</v>
-      </c>
-      <c r="O10" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.Vacuo</v>
-      </c>
-      <c r="P10" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q10" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U10" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V10" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W10" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z10" s="35" t="s">
-        <v>249</v>
+        <v>190</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3163,86 +3255,86 @@
       <c r="B11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="34" t="str">
+      <c r="C11" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M11" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N11" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema de Gás Hospitalar</v>
+      </c>
+      <c r="O11" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M11" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N11" s="34" t="str">
+        <v>Sistema.Óxido.Nitroso</v>
+      </c>
+      <c r="P11" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q11" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U11" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V11" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W11" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O11" s="30" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
-        <v>Queimador</v>
-      </c>
-      <c r="P11" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q11" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T11" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U11" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V11" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W11" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-11</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z11" s="35" t="s">
-        <v>247</v>
+        <v>191</v>
+      </c>
+      <c r="Z11" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3252,86 +3344,86 @@
       <c r="B12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="34" t="str">
+      <c r="C12" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M12" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N12" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema de Gás Hospitalar</v>
+      </c>
+      <c r="O12" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M12" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N12" s="34" t="str">
+        <v>Sistema.Nitrogênio</v>
+      </c>
+      <c r="P12" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q12" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V12" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W12" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O12" s="30" t="str">
-        <f t="shared" ref="O12:O25" si="16">IF(ISNUMBER(FIND("Ifc",F12)),CONCATENATE("Classe IFC:   ",F12),CONCATENATE("",F12))</f>
-        <v>Registro.de.Gás</v>
-      </c>
-      <c r="P12" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q12" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T12" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U12" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V12" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W12" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z12" s="35" t="s">
-        <v>247</v>
+        <v>191</v>
+      </c>
+      <c r="Z12" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3341,86 +3433,86 @@
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="34" t="str">
+      <c r="C13" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="33" t="str">
+        <f t="shared" ref="L13" si="15">CONCATENATE("", C13)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M13" s="33" t="str">
+        <f t="shared" ref="M13" si="16">CONCATENATE("", D13)</f>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N13" s="33" t="str">
+        <f t="shared" ref="N13" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <v>Sistema de Gás Hospitalar</v>
+      </c>
+      <c r="O13" s="30" t="str">
         <f t="shared" si="8"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M13" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N13" s="34" t="str">
+        <v>Sistema.Hélio</v>
+      </c>
+      <c r="P13" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q13" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T13" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U13" s="35" t="str">
+        <f t="shared" ref="U13" si="18">SUBSTITUTE(E13, "_", " ")</f>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V13" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W13" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O13" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Válvula.de.Gás</v>
-      </c>
-      <c r="P13" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q13" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T13" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U13" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V13" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W13" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-13</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z13" s="35" t="s">
-        <v>247</v>
+        <v>191</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3430,86 +3522,86 @@
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="34" t="str">
-        <f t="shared" ref="L14" si="17">CONCATENATE("", C14)</f>
+      <c r="C14" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M14" s="34" t="str">
-        <f t="shared" ref="M14" si="18">CONCATENATE("", D14)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N14" s="34" t="str">
-        <f t="shared" ref="N14" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E14),"."," ")," De "," de "))</f>
-        <v>Peças Gás</v>
+      <c r="M14" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N14" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Medidor.de.Gás</v>
-      </c>
-      <c r="P14" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q14" s="59" t="s">
+        <f t="shared" si="8"/>
+        <v>Sistema.Vacuo</v>
+      </c>
+      <c r="P14" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q14" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="R14" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T14" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U14" s="36" t="str">
-        <f t="shared" ref="U14" si="20">SUBSTITUTE(E14, "_", " ")</f>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V14" s="36" t="s">
-        <v>118</v>
+      <c r="T14" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U14" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V14" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W14" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-14</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z14" s="35" t="s">
-        <v>247</v>
+        <v>194</v>
+      </c>
+      <c r="Z14" s="34" t="s">
+        <v>245</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3519,86 +3611,86 @@
       <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="48" t="s">
-        <v>116</v>
+      <c r="C15" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="G15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="34" t="str">
-        <f t="shared" si="8"/>
+      <c r="E15" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M15" s="34" t="str">
-        <f t="shared" si="9"/>
+      <c r="M15" s="33" t="str">
+        <f t="shared" si="12"/>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N15" s="34" t="str">
+      <c r="N15" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O15" s="30" t="str">
+        <f>IF(ISNUMBER(FIND("Ifc",F15)),CONCATENATE("Classe IFC:   ",F15),CONCATENATE("",F15))</f>
+        <v>Queimador</v>
+      </c>
+      <c r="P15" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q15" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U15" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W15" s="66" t="str">
         <f t="shared" si="10"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O15" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Acessório.de.Gás</v>
-      </c>
-      <c r="P15" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q15" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T15" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U15" s="36" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V15" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W15" s="66" t="str">
-        <f t="shared" si="7"/>
         <v>Key-GAS-15</v>
       </c>
       <c r="X15" s="29" t="s">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="Z15" s="35" t="s">
-        <v>247</v>
+        <v>165</v>
+      </c>
+      <c r="Z15" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3608,86 +3700,86 @@
       <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>116</v>
+      <c r="C16" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="34" t="str">
-        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M16" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="12"/>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N16" s="34" t="str">
-        <f t="shared" si="2"/>
+      <c r="N16" s="33" t="str">
+        <f t="shared" si="13"/>
         <v>Peças Gás</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Buchão.de.Gás</v>
-      </c>
-      <c r="P16" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q16" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="R16" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T16" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U16" s="36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="O16:O29" si="19">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
+        <v>Registro.de.Gás</v>
+      </c>
+      <c r="P16" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q16" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="R16" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T16" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U16" s="35" t="str">
+        <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V16" s="36" t="s">
-        <v>118</v>
+      <c r="V16" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W16" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z16" s="35" t="s">
-        <v>247</v>
+        <v>115</v>
+      </c>
+      <c r="Z16" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3697,86 +3789,86 @@
       <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>116</v>
+      <c r="C17" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="34" t="str">
-        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M17" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="12"/>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N17" s="34" t="str">
-        <f t="shared" si="2"/>
+      <c r="N17" s="33" t="str">
+        <f t="shared" si="13"/>
         <v>Peças Gás</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Cilindro.de.Gás</v>
-      </c>
-      <c r="P17" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q17" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="R17" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T17" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U17" s="36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
+        <v>Válvula.de.Gás</v>
+      </c>
+      <c r="P17" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q17" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="R17" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T17" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U17" s="35" t="str">
+        <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V17" s="36" t="s">
-        <v>118</v>
+      <c r="V17" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W17" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z17" s="35" t="s">
-        <v>247</v>
+        <v>115</v>
+      </c>
+      <c r="Z17" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3786,86 +3878,86 @@
       <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>116</v>
+      <c r="C18" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E18" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="34" t="str">
-        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="33" t="str">
+        <f t="shared" ref="L18" si="20">CONCATENATE("", C18)</f>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M18" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="M18" s="33" t="str">
+        <f t="shared" ref="M18" si="21">CONCATENATE("", D18)</f>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N18" s="34" t="str">
-        <f t="shared" si="2"/>
+      <c r="N18" s="33" t="str">
+        <f t="shared" ref="N18" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
         <v>Peças Gás</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Tanque.de.Gás</v>
-      </c>
-      <c r="P18" s="59" t="s">
+        <f t="shared" si="19"/>
+        <v>Medidor.de.Gás</v>
+      </c>
+      <c r="P18" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="Q18" s="59" t="s">
-        <v>241</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T18" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U18" s="36" t="str">
-        <f t="shared" si="5"/>
+      <c r="Q18" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="R18" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T18" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U18" s="35" t="str">
+        <f t="shared" ref="U18" si="23">SUBSTITUTE(E18, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
-      <c r="V18" s="36" t="s">
-        <v>118</v>
+      <c r="V18" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W18" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-18</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z18" s="35" t="s">
-        <v>247</v>
+        <v>195</v>
+      </c>
+      <c r="Z18" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3875,86 +3967,86 @@
       <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="48" t="s">
-        <v>116</v>
+      <c r="C19" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="34" t="str">
-        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="33" t="str">
+        <f t="shared" si="11"/>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M19" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="M19" s="33" t="str">
+        <f t="shared" si="12"/>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N19" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
+      <c r="N19" s="33" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças Gás</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Aquecedor.a.Gás</v>
-      </c>
-      <c r="P19" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q19" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T19" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U19" s="36" t="str">
-        <f t="shared" si="5"/>
-        <v>Gás.Doméstico</v>
-      </c>
-      <c r="V19" s="36" t="s">
-        <v>118</v>
+        <f t="shared" si="19"/>
+        <v>Acessório.de.Gás</v>
+      </c>
+      <c r="P19" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q19" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="R19" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T19" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U19" s="35" t="str">
+        <f t="shared" si="14"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V19" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="W19" s="66" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Key-GAS-19</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z19" s="35" t="s">
-        <v>247</v>
+        <v>196</v>
+      </c>
+      <c r="Z19" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3964,86 +4056,86 @@
       <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M20" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N20" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O20" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Buchão.de.Gás</v>
+      </c>
+      <c r="P20" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="R20" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T20" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U20" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V20" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W20" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-20</v>
+      </c>
+      <c r="X20" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y20" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M20" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N20" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
-      </c>
-      <c r="O20" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Boiler.a.Gás</v>
-      </c>
-      <c r="P20" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q20" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="R20" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T20" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U20" s="36" t="str">
-        <f t="shared" si="5"/>
-        <v>Gás.Doméstico</v>
-      </c>
-      <c r="V20" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W20" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-20</v>
-      </c>
-      <c r="X20" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y20" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z20" s="35" t="s">
-        <v>247</v>
+      <c r="Z20" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4053,86 +4145,86 @@
       <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L21" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M21" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N21" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O21" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Cilindro.de.Gás</v>
+      </c>
+      <c r="P21" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q21" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="R21" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T21" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U21" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V21" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W21" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-21</v>
+      </c>
+      <c r="X21" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y21" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L21" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M21" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N21" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Gás Doméstico</v>
-      </c>
-      <c r="O21" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Caldeira.a.Gás</v>
-      </c>
-      <c r="P21" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q21" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="R21" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T21" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U21" s="36" t="str">
-        <f t="shared" si="5"/>
-        <v>Gás.Doméstico</v>
-      </c>
-      <c r="V21" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W21" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-21</v>
-      </c>
-      <c r="X21" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y21" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z21" s="35" t="s">
-        <v>247</v>
+      <c r="Z21" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4142,86 +4234,86 @@
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L22" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M22" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N22" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O22" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Tanque.de.Gás</v>
+      </c>
+      <c r="P22" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q22" s="58" t="s">
+        <v>237</v>
+      </c>
+      <c r="R22" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T22" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U22" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V22" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W22" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-22</v>
+      </c>
+      <c r="X22" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y22" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L22" s="34" t="str">
-        <f t="shared" ref="L22" si="21">CONCATENATE("", C22)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M22" s="34" t="str">
-        <f t="shared" ref="M22" si="22">CONCATENATE("", D22)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N22" s="34" t="str">
-        <f t="shared" ref="N22" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
-        <v>Gás Doméstico</v>
-      </c>
-      <c r="O22" s="30" t="str">
-        <f t="shared" ref="O22" si="24">IF(ISNUMBER(FIND("Ifc",F22)),CONCATENATE("Classe IFC:   ",F22),CONCATENATE("",F22))</f>
-        <v>Tubulação.Gás</v>
-      </c>
-      <c r="P22" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q22" s="59" t="s">
-        <v>161</v>
-      </c>
-      <c r="R22" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T22" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U22" s="36" t="str">
-        <f t="shared" ref="U22" si="25">SUBSTITUTE(E22, "_", " ")</f>
-        <v>Gás.Doméstico</v>
-      </c>
-      <c r="V22" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W22" s="66" t="str">
-        <f t="shared" ref="W22" si="26">CONCATENATE("Key-GAS-",A22)</f>
-        <v>Key-GAS-22</v>
-      </c>
-      <c r="X22" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y22" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z22" s="35" t="s">
-        <v>247</v>
+      <c r="Z22" s="34" t="s">
+        <v>243</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4231,86 +4323,86 @@
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>116</v>
+      <c r="C23" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E23" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M23" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N23" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Gás Doméstico</v>
+      </c>
+      <c r="O23" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Aquecedor.a.Gás</v>
+      </c>
+      <c r="P23" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q23" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="R23" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T23" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U23" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Gás.Doméstico</v>
+      </c>
+      <c r="V23" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W23" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-23</v>
+      </c>
+      <c r="X23" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y23" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z23" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F23" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="34" t="str">
-        <f t="shared" ref="L23:L25" si="27">CONCATENATE("", C23)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M23" s="34" t="str">
-        <f t="shared" ref="M23:M25" si="28">CONCATENATE("", D23)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N23" s="34" t="str">
-        <f t="shared" ref="N23:N25" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E23),"."," ")," De "," de "))</f>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O23" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Aquecedor.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P23" s="59" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q23" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="R23" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T23" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U23" s="36" t="str">
-        <f t="shared" ref="U23:U25" si="30">SUBSTITUTE(E23, "_", " ")</f>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V23" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W23" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-23</v>
-      </c>
-      <c r="X23" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y23" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z23" s="35" t="s">
-        <v>249</v>
-      </c>
       <c r="AA23" s="30" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4320,86 +4412,86 @@
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="48" t="s">
-        <v>116</v>
+      <c r="C24" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E24" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M24" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N24" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Gás Doméstico</v>
+      </c>
+      <c r="O24" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Boiler.a.Gás</v>
+      </c>
+      <c r="P24" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q24" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="R24" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T24" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U24" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Gás.Doméstico</v>
+      </c>
+      <c r="V24" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W24" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-24</v>
+      </c>
+      <c r="X24" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y24" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z24" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F24" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="34" t="str">
-        <f t="shared" si="27"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M24" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N24" s="34" t="str">
-        <f t="shared" si="29"/>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O24" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Boiler.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P24" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q24" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="R24" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T24" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U24" s="36" t="str">
-        <f t="shared" si="30"/>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V24" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W24" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-24</v>
-      </c>
-      <c r="X24" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y24" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z24" s="35" t="s">
-        <v>249</v>
-      </c>
       <c r="AA24" s="30" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4409,86 +4501,86 @@
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>116</v>
+      <c r="C25" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E25" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M25" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N25" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Gás Doméstico</v>
+      </c>
+      <c r="O25" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Caldeira.a.Gás</v>
+      </c>
+      <c r="P25" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q25" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="R25" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T25" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U25" s="35" t="str">
+        <f t="shared" si="9"/>
+        <v>Gás.Doméstico</v>
+      </c>
+      <c r="V25" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W25" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-25</v>
+      </c>
+      <c r="X25" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y25" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z25" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F25" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L25" s="34" t="str">
-        <f t="shared" si="27"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M25" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N25" s="34" t="str">
-        <f t="shared" si="29"/>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O25" s="30" t="str">
-        <f t="shared" si="16"/>
-        <v>Caldeira.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P25" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q25" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="R25" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T25" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U25" s="36" t="str">
-        <f t="shared" si="30"/>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V25" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W25" s="66" t="str">
-        <f t="shared" si="7"/>
-        <v>Key-GAS-25</v>
-      </c>
-      <c r="X25" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y25" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z25" s="35" t="s">
-        <v>249</v>
-      </c>
       <c r="AA25" s="30" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4498,114 +4590,488 @@
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="48" t="s">
-        <v>116</v>
+      <c r="C26" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E26" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" ref="L26" si="24">CONCATENATE("", C26)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M26" s="33" t="str">
+        <f t="shared" ref="M26" si="25">CONCATENATE("", D26)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N26" s="33" t="str">
+        <f t="shared" ref="N26" si="26">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E26),"."," ")," De "," de "))</f>
+        <v>Gás Doméstico</v>
+      </c>
+      <c r="O26" s="30" t="str">
+        <f t="shared" ref="O26" si="27">IF(ISNUMBER(FIND("Ifc",F26)),CONCATENATE("Classe IFC:   ",F26),CONCATENATE("",F26))</f>
+        <v>Tubulação.Gás</v>
+      </c>
+      <c r="P26" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q26" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="R26" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T26" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U26" s="35" t="str">
+        <f t="shared" ref="U26" si="28">SUBSTITUTE(E26, "_", " ")</f>
+        <v>Gás.Doméstico</v>
+      </c>
+      <c r="V26" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W26" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-26</v>
+      </c>
+      <c r="X26" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y26" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z26" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F26" s="48" t="s">
+      <c r="AA26" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" ref="L27:L29" si="29">CONCATENATE("", C27)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" ref="M27:M29" si="30">CONCATENATE("", D27)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N27" s="33" t="str">
+        <f t="shared" ref="N27:N29" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Aquecedor.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P27" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q27" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="R27" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T27" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U27" s="35" t="str">
+        <f t="shared" ref="U27:U29" si="32">SUBSTITUTE(E27, "_", " ")</f>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V27" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W27" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-27</v>
+      </c>
+      <c r="X27" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y27" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z27" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA27" s="30" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N28" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Boiler.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P28" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q28" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="R28" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T28" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U28" s="35" t="str">
+        <f t="shared" si="32"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V28" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W28" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-28</v>
+      </c>
+      <c r="X28" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y28" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z28" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA28" s="30" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M29" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N29" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O29" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Caldeira.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P29" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q29" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="R29" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T29" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U29" s="35" t="str">
+        <f t="shared" si="32"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V29" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W29" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-29</v>
+      </c>
+      <c r="X29" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y29" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z29" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA29" s="30" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="32">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
+        <f t="shared" ref="L30" si="33">CONCATENATE("", C30)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M30" s="33" t="str">
+        <f t="shared" ref="M30" si="34">CONCATENATE("", D30)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N30" s="33" t="str">
+        <f t="shared" ref="N30" si="35">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O30" s="30" t="str">
+        <f t="shared" ref="O30" si="36">IF(ISNUMBER(FIND("Ifc",F30)),CONCATENATE("Classe IFC:   ",F30),CONCATENATE("",F30))</f>
+        <v>Tubulação.Gás.Hospitalar</v>
+      </c>
+      <c r="P30" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="G26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="34" t="str">
-        <f t="shared" ref="L26" si="31">CONCATENATE("", C26)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M26" s="34" t="str">
-        <f t="shared" ref="M26" si="32">CONCATENATE("", D26)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N26" s="34" t="str">
-        <f t="shared" ref="N26" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E26),"."," ")," De "," de "))</f>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O26" s="30" t="str">
-        <f t="shared" ref="O26" si="34">IF(ISNUMBER(FIND("Ifc",F26)),CONCATENATE("Classe IFC:   ",F26),CONCATENATE("",F26))</f>
-        <v>Tubulação.Gás.Hospitalar</v>
-      </c>
-      <c r="P26" s="59" t="s">
+      <c r="Q30" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="Q26" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="R26" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="T26" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="U26" s="36" t="str">
-        <f t="shared" ref="U26" si="35">SUBSTITUTE(E26, "_", " ")</f>
+      <c r="R30" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="T30" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="U30" s="35" t="str">
+        <f t="shared" ref="U30" si="37">SUBSTITUTE(E30, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
-      <c r="V26" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="W26" s="66" t="str">
-        <f t="shared" ref="W26" si="36">CONCATENATE("Key-GAS-",A26)</f>
-        <v>Key-GAS-26</v>
-      </c>
-      <c r="X26" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y26" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z26" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA26" s="30" t="s">
-        <v>237</v>
+      <c r="V30" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W30" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v>Key-GAS-30</v>
+      </c>
+      <c r="X30" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y30" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z30" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA30" s="30" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA887">
-    <sortCondition ref="F2:F887"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AA891">
+    <sortCondition ref="F7:F891"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1 AA1:AA26">
-    <cfRule type="cellIs" dxfId="15" priority="36" operator="equal">
+  <conditionalFormatting sqref="AA7:AA30">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
+    <cfRule type="cellIs" dxfId="20" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1484"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F3 F11:F1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="1494"/>
+  <conditionalFormatting sqref="F15:F1048576 F1 F7">
+    <cfRule type="duplicateValues" dxfId="18" priority="1506"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="12" priority="1471"/>
+  <conditionalFormatting sqref="F31:F1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1477"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27:F1048576 F2">
-    <cfRule type="duplicateValues" dxfId="11" priority="1465"/>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27:F1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1444"/>
+  <conditionalFormatting sqref="A2:A30">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4820,7 +5286,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4880,7 +5346,7 @@
       <c r="G1" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="54" t="s">
         <v>77</v>
       </c>
       <c r="I1" s="19" t="s">
@@ -4922,54 +5388,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="56" t="s">
+      <c r="L2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="56" t="s">
+      <c r="N2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="56" t="s">
+      <c r="P2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="56" t="s">
+      <c r="R2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="24" t="s">
@@ -4981,182 +5447,182 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="39" t="s">
-        <v>104</v>
+      <c r="E3" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="H3" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="J3" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="J3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="56" t="s">
+      <c r="N3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="56" t="s">
+      <c r="R3" s="55" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="54" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>201</v>
+      <c r="B4" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>197</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="H4" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="P4" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="56" t="s">
+      <c r="Q4" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="R4" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M4" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N4" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="P4" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="R4" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S4" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>201</v>
+      <c r="B5" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>197</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="H5" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" s="55" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="P5" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="L5" s="56" t="s">
+      <c r="Q5" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="M5" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="N5" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="P5" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="R5" s="56" t="s">
-        <v>110</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5226,22 +5692,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/GASE/Ontologia_Gases.xlsx
+++ b/Versão5/GASE/Ontologia_Gases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232CD4FE-6666-41B3-8700-696DCC2C68CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF060DC-378A-4164-B22E-743D3E2F385D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -377,12 +377,6 @@
     <t>CTI_Projeto_01</t>
   </si>
   <si>
-    <t>fabricante</t>
-  </si>
-  <si>
-    <t>fornecedor</t>
-  </si>
-  <si>
     <t>código.abnt</t>
   </si>
   <si>
@@ -852,6 +846,12 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>quem.fabricou</t>
+  </si>
+  <si>
+    <t>quem.forneceu</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1392,20 +1392,11 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
@@ -1482,6 +1473,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1519,14 +1518,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2072,7 +2063,7 @@
         <v>49</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>94</v>
@@ -2228,7 +2219,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>94</v>
@@ -2240,7 +2231,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46139.495710648145</v>
+        <v>46213.811803124998</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>94</v>
@@ -2284,7 +2275,7 @@
         <v>72</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C22" s="44" t="s">
         <v>94</v>
@@ -2295,7 +2286,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>95</v>
@@ -2342,7 +2333,7 @@
     <col min="20" max="20" width="7.23046875" customWidth="1"/>
     <col min="21" max="21" width="10.84375" customWidth="1"/>
     <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="67" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" customWidth="1"/>
     <col min="24" max="24" width="53" style="60" customWidth="1"/>
     <col min="25" max="25" width="18.23046875" style="61" customWidth="1"/>
     <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
@@ -2437,7 +2428,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>84</v>
@@ -2446,10 +2437,10 @@
         <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>9</v>
@@ -2483,7 +2474,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>86</v>
@@ -2504,7 +2495,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W2" s="66" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-GAS-",A2)</f>
@@ -2529,7 +2520,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>84</v>
@@ -2538,10 +2529,10 @@
         <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>9</v>
@@ -2575,7 +2566,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>86</v>
@@ -2596,7 +2587,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W3" s="66" t="str">
         <f t="shared" si="3"/>
@@ -2621,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C4" s="64" t="s">
         <v>84</v>
@@ -2630,10 +2621,10 @@
         <v>85</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>9</v>
@@ -2667,7 +2658,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>86</v>
@@ -2688,7 +2679,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W4" s="66" t="str">
         <f t="shared" si="3"/>
@@ -2713,7 +2704,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C5" s="64" t="s">
         <v>84</v>
@@ -2722,10 +2713,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>9</v>
@@ -2759,7 +2750,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>86</v>
@@ -2780,7 +2771,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W5" s="66" t="str">
         <f t="shared" si="3"/>
@@ -2805,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C6" s="64" t="s">
         <v>84</v>
@@ -2814,10 +2805,10 @@
         <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>9</v>
@@ -2851,7 +2842,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>86</v>
@@ -2872,7 +2863,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W6" s="66" t="str">
         <f t="shared" si="3"/>
@@ -2900,16 +2891,16 @@
         <v>44</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>9</v>
@@ -2943,42 +2934,42 @@
         <v>Sistema.GAS</v>
       </c>
       <c r="P7" s="58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R7" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T7" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U7" s="35" t="str">
         <f t="shared" ref="U7:U25" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.de.Gás</v>
       </c>
       <c r="V7" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W7" s="66" t="str">
         <f t="shared" ref="W7:W30" si="10">CONCATENATE("Key-GAS-",A7)</f>
         <v>Key-GAS-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z7" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -2989,16 +2980,16 @@
         <v>44</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>9</v>
@@ -3032,42 +3023,42 @@
         <v>Sistema.Oxigênio</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q8" s="58" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R8" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T8" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U8" s="35" t="str">
         <f t="shared" ref="U8:U19" si="14">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V8" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W8" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z8" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3078,16 +3069,16 @@
         <v>44</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>9</v>
@@ -3121,42 +3112,42 @@
         <v>Sistema.Ar.Medicinal</v>
       </c>
       <c r="P9" s="58" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q9" s="58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R9" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T9" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U9" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V9" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W9" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z9" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3167,16 +3158,16 @@
         <v>44</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F10" s="63" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>9</v>
@@ -3210,42 +3201,42 @@
         <v>Sistema.Ar.Comprimido</v>
       </c>
       <c r="P10" s="58" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q10" s="58" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R10" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T10" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U10" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V10" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W10" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Z10" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3256,16 +3247,16 @@
         <v>44</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>9</v>
@@ -3299,42 +3290,42 @@
         <v>Sistema.Óxido.Nitroso</v>
       </c>
       <c r="P11" s="58" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="Q11" s="58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R11" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T11" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U11" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W11" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-11</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z11" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3345,16 +3336,16 @@
         <v>44</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F12" s="63" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>9</v>
@@ -3388,42 +3379,42 @@
         <v>Sistema.Nitrogênio</v>
       </c>
       <c r="P12" s="58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="58" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R12" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T12" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U12" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V12" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W12" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z12" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3434,16 +3425,16 @@
         <v>44</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G13" s="37" t="s">
         <v>9</v>
@@ -3477,42 +3468,42 @@
         <v>Sistema.Hélio</v>
       </c>
       <c r="P13" s="58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="Q13" s="58" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R13" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T13" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U13" s="35" t="str">
         <f t="shared" ref="U13" si="18">SUBSTITUTE(E13, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V13" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W13" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-13</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z13" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3523,16 +3514,16 @@
         <v>44</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>9</v>
@@ -3566,42 +3557,42 @@
         <v>Sistema.Vacuo</v>
       </c>
       <c r="P14" s="58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q14" s="58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="R14" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T14" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U14" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V14" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W14" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-14</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Z14" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3612,16 +3603,16 @@
         <v>44</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>9</v>
@@ -3655,42 +3646,42 @@
         <v>Queimador</v>
       </c>
       <c r="P15" s="58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q15" s="58" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="R15" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T15" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U15" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V15" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W15" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-15</v>
       </c>
       <c r="X15" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Z15" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3701,16 +3692,16 @@
         <v>44</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>9</v>
@@ -3744,42 +3735,42 @@
         <v>Registro.de.Gás</v>
       </c>
       <c r="P16" s="58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R16" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T16" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U16" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V16" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W16" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z16" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3790,16 +3781,16 @@
         <v>44</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>9</v>
@@ -3833,42 +3824,42 @@
         <v>Válvula.de.Gás</v>
       </c>
       <c r="P17" s="58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q17" s="58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R17" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T17" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U17" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V17" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W17" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Z17" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3879,16 +3870,16 @@
         <v>44</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F18" s="47" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>9</v>
@@ -3922,42 +3913,42 @@
         <v>Medidor.de.Gás</v>
       </c>
       <c r="P18" s="58" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q18" s="58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R18" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T18" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U18" s="35" t="str">
         <f t="shared" ref="U18" si="23">SUBSTITUTE(E18, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W18" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-18</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Z18" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -3968,16 +3959,16 @@
         <v>44</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>9</v>
@@ -4011,42 +4002,42 @@
         <v>Acessório.de.Gás</v>
       </c>
       <c r="P19" s="58" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q19" s="58" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R19" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T19" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U19" s="35" t="str">
         <f t="shared" si="14"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V19" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W19" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-19</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Z19" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4057,16 +4048,16 @@
         <v>44</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G20" s="37" t="s">
         <v>9</v>
@@ -4100,42 +4091,42 @@
         <v>Buchão.de.Gás</v>
       </c>
       <c r="P20" s="58" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q20" s="58" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="R20" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T20" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U20" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V20" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W20" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-20</v>
       </c>
       <c r="X20" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Z20" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4146,16 +4137,16 @@
         <v>44</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E21" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="47" t="s">
         <v>129</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>131</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>9</v>
@@ -4189,42 +4180,42 @@
         <v>Cilindro.de.Gás</v>
       </c>
       <c r="P21" s="58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q21" s="58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R21" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T21" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U21" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V21" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W21" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-21</v>
       </c>
       <c r="X21" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Z21" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4235,16 +4226,16 @@
         <v>44</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>9</v>
@@ -4278,42 +4269,42 @@
         <v>Tanque.de.Gás</v>
       </c>
       <c r="P22" s="58" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="Q22" s="58" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R22" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T22" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U22" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V22" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W22" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-22</v>
       </c>
       <c r="X22" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Z22" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4324,16 +4315,16 @@
         <v>44</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F23" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>9</v>
@@ -4367,42 +4358,42 @@
         <v>Aquecedor.a.Gás</v>
       </c>
       <c r="P23" s="58" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q23" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="R23" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="R23" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="35" t="s">
-        <v>164</v>
-      </c>
       <c r="T23" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U23" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V23" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W23" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z23" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4413,16 +4404,16 @@
         <v>44</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>9</v>
@@ -4456,42 +4447,42 @@
         <v>Boiler.a.Gás</v>
       </c>
       <c r="P24" s="58" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q24" s="58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="R24" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S24" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T24" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U24" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V24" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W24" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z24" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4502,16 +4493,16 @@
         <v>44</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>9</v>
@@ -4545,42 +4536,42 @@
         <v>Caldeira.a.Gás</v>
       </c>
       <c r="P25" s="58" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q25" s="58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R25" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T25" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U25" s="35" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V25" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W25" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Z25" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4591,16 +4582,16 @@
         <v>44</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>9</v>
@@ -4634,42 +4625,42 @@
         <v>Tubulação.Gás</v>
       </c>
       <c r="P26" s="58" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q26" s="58" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R26" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T26" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U26" s="35" t="str">
         <f t="shared" ref="U26" si="28">SUBSTITUTE(E26, "_", " ")</f>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V26" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W26" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-26</v>
       </c>
       <c r="X26" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y26" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Z26" s="34" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4680,16 +4671,16 @@
         <v>44</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>9</v>
@@ -4723,42 +4714,42 @@
         <v>Aquecedor.a.Gás.Hospitalar</v>
       </c>
       <c r="P27" s="58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q27" s="58" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R27" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T27" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U27" s="35" t="str">
         <f t="shared" ref="U27:U29" si="32">SUBSTITUTE(E27, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V27" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W27" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z27" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4769,16 +4760,16 @@
         <v>44</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G28" s="37" t="s">
         <v>9</v>
@@ -4812,42 +4803,42 @@
         <v>Boiler.a.Gás.Hospitalar</v>
       </c>
       <c r="P28" s="58" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q28" s="58" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="R28" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S28" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T28" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U28" s="35" t="str">
         <f t="shared" si="32"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V28" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W28" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Z28" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4858,16 +4849,16 @@
         <v>44</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G29" s="37" t="s">
         <v>9</v>
@@ -4901,42 +4892,42 @@
         <v>Caldeira.a.Gás.Hospitalar</v>
       </c>
       <c r="P29" s="58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q29" s="58" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R29" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T29" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U29" s="35" t="str">
         <f t="shared" si="32"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V29" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W29" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-29</v>
       </c>
       <c r="X29" s="29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Y29" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Z29" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA29" s="30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4947,16 +4938,16 @@
         <v>44</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>9</v>
@@ -4990,42 +4981,42 @@
         <v>Tubulação.Gás.Hospitalar</v>
       </c>
       <c r="P30" s="58" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Q30" s="58" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R30" s="34" t="s">
         <v>9</v>
       </c>
       <c r="S30" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T30" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U30" s="35" t="str">
         <f t="shared" ref="U30" si="37">SUBSTITUTE(E30, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V30" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W30" s="66" t="str">
         <f t="shared" si="10"/>
         <v>Key-GAS-30</v>
       </c>
       <c r="X30" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Y30" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Z30" s="34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -5033,45 +5024,38 @@
     <sortCondition ref="F7:F891"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA7:AA30">
-    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:A30">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
-    <cfRule type="cellIs" dxfId="20" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="19" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1484"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="18" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1456"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1477"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA30">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A30">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5286,7 +5270,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5313,9 +5297,9 @@
     <col min="7" max="7" width="62.3828125" customWidth="1"/>
     <col min="8" max="8" width="5.3046875" customWidth="1"/>
     <col min="9" max="9" width="17.07421875" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" customWidth="1"/>
+    <col min="10" max="10" width="7.3828125" customWidth="1"/>
     <col min="11" max="11" width="4.765625" customWidth="1"/>
-    <col min="12" max="12" width="5.3046875" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.4609375" customWidth="1"/>
     <col min="14" max="15" width="6.4609375" customWidth="1"/>
     <col min="16" max="16" width="5.3828125" customWidth="1"/>
@@ -5391,7 +5375,7 @@
         <v>100</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>9</v>
@@ -5403,7 +5387,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H2" s="55" t="s">
         <v>9</v>
@@ -5447,10 +5431,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>83</v>
@@ -5462,13 +5446,13 @@
         <v>78</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H3" s="55" t="s">
         <v>78</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J3" s="55" t="s">
         <v>9</v>
@@ -5498,7 +5482,7 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5506,22 +5490,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H4" s="55" t="s">
         <v>9</v>
@@ -5530,34 +5514,34 @@
         <v>9</v>
       </c>
       <c r="J4" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N4" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="L4" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M4" s="24" t="s">
+      <c r="O4" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="P4" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="R4" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="P4" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="R4" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S4" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
@@ -5565,22 +5549,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H5" s="55" t="s">
         <v>9</v>
@@ -5589,40 +5573,40 @@
         <v>9</v>
       </c>
       <c r="J5" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="N5" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="M5" s="24" t="s">
+      <c r="O5" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="P5" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="R5" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="N5" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="P5" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="R5" s="55" t="s">
-        <v>106</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="7" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5692,22 +5676,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/GASE/Ontologia_Gases.xlsx
+++ b/Versão5/GASE/Ontologia_Gases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF060DC-378A-4164-B22E-743D3E2F385D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3829E4B-A671-4F0B-9FAB-523F4D23BAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46213.811803124998</v>
+        <v>46214.376720949076</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>94</v>
@@ -5301,10 +5301,11 @@
     <col min="11" max="11" width="4.765625" customWidth="1"/>
     <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.4609375" customWidth="1"/>
-    <col min="14" max="15" width="6.4609375" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
+    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.4609375" customWidth="1"/>
+    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.765625" customWidth="1"/>
+    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.3046875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Versão5/GASE/Ontologia_Gases.xlsx
+++ b/Versão5/GASE/Ontologia_Gases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3829E4B-A671-4F0B-9FAB-523F4D23BAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CFD370-80D6-47AF-8887-3C29090B4EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="259">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -203,9 +203,6 @@
     <t>000 Traducción Classe 5</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Chave</t>
   </si>
   <si>
@@ -809,21 +806,12 @@
     <t>[ OST_PipeAccessory ]</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
@@ -852,6 +840,15 @@
   </si>
   <si>
     <t>quem.forneceu</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1293,18 +1290,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1329,9 +1314,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1344,9 +1326,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1381,22 +1360,92 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2028,280 +2077,280 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="40.07421875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="62"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="B2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C5" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="41" t="s">
+      <c r="B8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="14" t="s">
+      <c r="B11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="14" t="s">
+      <c r="B12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="14" t="s">
+      <c r="B13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
+      <c r="B14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
+      <c r="B15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="14" t="s">
+      <c r="B17" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46214.376720949076</v>
-      </c>
-      <c r="C18" s="44" t="s">
+        <v>46216.380840972219</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="42" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Household and Hospital Gas Objects</v>
       </c>
-      <c r="C24" s="44" t="s">
-        <v>96</v>
+      <c r="C24" s="40" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2313,153 +2362,154 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA30"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.765625" customWidth="1"/>
-    <col min="4" max="4" width="9.07421875" customWidth="1"/>
-    <col min="5" max="5" width="11.53515625" customWidth="1"/>
-    <col min="6" max="6" width="11.765625" style="46" customWidth="1"/>
-    <col min="7" max="11" width="6.3046875" style="36" customWidth="1"/>
-    <col min="12" max="12" width="7.4609375" customWidth="1"/>
-    <col min="13" max="13" width="5.3046875" customWidth="1"/>
-    <col min="14" max="14" width="10.921875" customWidth="1"/>
-    <col min="15" max="15" width="11.3828125" customWidth="1"/>
-    <col min="16" max="16" width="28.84375" customWidth="1"/>
-    <col min="17" max="17" width="29.23046875" customWidth="1"/>
-    <col min="18" max="18" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.921875" customWidth="1"/>
-    <col min="20" max="20" width="7.23046875" customWidth="1"/>
-    <col min="21" max="21" width="10.84375" customWidth="1"/>
-    <col min="22" max="22" width="5.921875" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" customWidth="1"/>
-    <col min="24" max="24" width="53" style="60" customWidth="1"/>
-    <col min="25" max="25" width="18.23046875" style="61" customWidth="1"/>
-    <col min="26" max="26" width="5.61328125" style="36" customWidth="1"/>
-    <col min="27" max="27" width="40.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.28515625" style="55" customWidth="1"/>
+    <col min="26" max="26" width="7.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="50" t="s">
+      <c r="M1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58">
         <v>2</v>
       </c>
-      <c r="J1" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="S1" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="U1" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="W1" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z1" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA1" s="40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="32">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C2" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>249</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="37" t="s">
+      <c r="E2" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2467,38 +2517,38 @@
       </c>
       <c r="N2" s="33" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q2" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="30" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="35" t="str">
+      <c r="U2" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W2" s="66" t="str">
-        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-GAS-",A2)</f>
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W2" s="59" t="str">
+        <f t="shared" ref="W2:W30" si="3">CONCATENATE("Key-GAS-",A2)</f>
         <v>Key-GAS-2</v>
       </c>
       <c r="X2" s="30" t="s">
@@ -2507,51 +2557,51 @@
       <c r="Y2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="34" t="s">
-        <v>9</v>
+      <c r="Z2" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F3" s="64" t="s">
-        <v>250</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="37" t="s">
+      <c r="E3" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2559,37 +2609,37 @@
       </c>
       <c r="N3" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="35" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W3" s="66" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W3" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-3</v>
       </c>
@@ -2599,7 +2649,7 @@
       <c r="Y3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="34" t="s">
+      <c r="Z3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="30" t="str">
@@ -2607,43 +2657,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="58">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>252</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="37" t="s">
+      <c r="G4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2651,37 +2701,37 @@
       </c>
       <c r="N4" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="35" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W4" s="66" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W4" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-4</v>
       </c>
@@ -2691,7 +2741,7 @@
       <c r="Y4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="34" t="s">
+      <c r="Z4" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="30" t="str">
@@ -2699,43 +2749,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="58">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="37" t="s">
+      <c r="E5" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2743,37 +2793,37 @@
       </c>
       <c r="N5" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="35" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W5" s="66" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W5" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-5</v>
       </c>
@@ -2783,7 +2833,7 @@
       <c r="Y5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="34" t="s">
+      <c r="Z5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="30" t="str">
@@ -2791,43 +2841,43 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="58">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>256</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="37" t="s">
+      <c r="E6" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>252</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="33" t="str">
         <f t="shared" si="0"/>
@@ -2835,37 +2885,37 @@
       </c>
       <c r="N6" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="33" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="35" t="str">
+        <v>85</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="35" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="35" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W6" s="66" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W6" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-6</v>
       </c>
@@ -2875,7 +2925,7 @@
       <c r="Y6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="34" t="s">
+      <c r="Z6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="30" t="str">
@@ -2883,38 +2933,38 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32">
+    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="58">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="F7" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
@@ -2933,1145 +2983,1145 @@
         <f t="shared" ref="O7:O14" si="8">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
         <v>Sistema.GAS</v>
       </c>
-      <c r="P7" s="58" t="s">
+      <c r="P7" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q7" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="Q7" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T7" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U7" s="35" t="str">
+      <c r="R7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U7" s="30" t="str">
         <f t="shared" ref="U7:U25" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.de.Gás</v>
       </c>
-      <c r="V7" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W7" s="66" t="str">
-        <f t="shared" ref="W7:W30" si="10">CONCATENATE("Key-GAS-",A7)</f>
+      <c r="V7" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W7" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z7" s="34" t="s">
-        <v>241</v>
+        <v>188</v>
+      </c>
+      <c r="Z7" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" ref="L8:L19" si="11">CONCATENATE("", C8)</f>
+        <f t="shared" ref="L8:L19" si="10">CONCATENATE("", C8)</f>
         <v>Sistema.Predial</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" ref="M8:M19" si="12">CONCATENATE("", D8)</f>
+        <f t="shared" ref="M8:M19" si="11">CONCATENATE("", D8)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N8" s="33" t="str">
-        <f t="shared" ref="N8:N19" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N8:N19" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O8" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Oxigênio</v>
       </c>
-      <c r="P8" s="58" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q8" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T8" s="35" t="s">
+      <c r="P8" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q8" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U8" s="30" t="str">
+        <f t="shared" ref="U8:U19" si="13">SUBSTITUTE(E8, "_", " ")</f>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V8" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U8" s="35" t="str">
-        <f t="shared" ref="U8:U19" si="14">SUBSTITUTE(E8, "_", " ")</f>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V8" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W8" s="66" t="str">
+      <c r="W8" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-8</v>
+      </c>
+      <c r="X8" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z8" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA8" s="30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="58">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-8</v>
-      </c>
-      <c r="X8" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y8" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="32">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M9" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M9" s="33" t="str">
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N9" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N9" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O9" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Ar.Medicinal</v>
       </c>
-      <c r="P9" s="58" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q9" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T9" s="35" t="s">
+      <c r="P9" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q9" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U9" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V9" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U9" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V9" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W9" s="66" t="str">
+      <c r="W9" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-9</v>
+      </c>
+      <c r="X9" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y9" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z9" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA9" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="58">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-9</v>
-      </c>
-      <c r="X9" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y9" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M10" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M10" s="33" t="str">
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N10" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N10" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O10" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Ar.Comprimido</v>
       </c>
-      <c r="P10" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q10" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T10" s="35" t="s">
+      <c r="P10" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q10" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U10" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V10" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U10" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V10" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W10" s="66" t="str">
+      <c r="W10" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-10</v>
+      </c>
+      <c r="X10" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y10" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA10" s="30" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="58">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-10</v>
-      </c>
-      <c r="X10" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y10" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="32">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="63" t="s">
-        <v>172</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M11" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M11" s="33" t="str">
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N11" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N11" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O11" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Óxido.Nitroso</v>
       </c>
-      <c r="P11" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q11" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T11" s="35" t="s">
+      <c r="P11" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U11" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V11" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U11" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V11" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W11" s="66" t="str">
+      <c r="W11" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-11</v>
+      </c>
+      <c r="X11" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z11" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA11" s="30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="58">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-11</v>
-      </c>
-      <c r="X11" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y11" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z11" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M12" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M12" s="33" t="str">
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N12" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N12" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O12" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Nitrogênio</v>
       </c>
-      <c r="P12" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q12" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="R12" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T12" s="35" t="s">
+      <c r="P12" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q12" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="R12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T12" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U12" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V12" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U12" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V12" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W12" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="W12" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z12" s="34" t="s">
-        <v>243</v>
+        <v>188</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>242</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="58">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F13" s="63" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="37" t="s">
+      <c r="F13" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
-        <f t="shared" ref="L13" si="15">CONCATENATE("", C13)</f>
+        <f t="shared" ref="L13" si="14">CONCATENATE("", C13)</f>
         <v>Sistema.Predial</v>
       </c>
       <c r="M13" s="33" t="str">
-        <f t="shared" ref="M13" si="16">CONCATENATE("", D13)</f>
+        <f t="shared" ref="M13" si="15">CONCATENATE("", D13)</f>
         <v>Sistema.Gases</v>
       </c>
       <c r="N13" s="33" t="str">
-        <f t="shared" ref="N13" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N13" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O13" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Hélio</v>
       </c>
-      <c r="P13" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q13" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="R13" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T13" s="35" t="s">
+      <c r="P13" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T13" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U13" s="30" t="str">
+        <f t="shared" ref="U13" si="17">SUBSTITUTE(E13, "_", " ")</f>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V13" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U13" s="35" t="str">
-        <f t="shared" ref="U13" si="18">SUBSTITUTE(E13, "_", " ")</f>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V13" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W13" s="66" t="str">
+      <c r="W13" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-13</v>
+      </c>
+      <c r="X13" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y13" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z13" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA13" s="30" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="58">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-13</v>
-      </c>
-      <c r="X13" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y13" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z13" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>190</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M14" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M14" s="33" t="str">
+        <v>Sistema.Gases</v>
+      </c>
+      <c r="N14" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Sistema.Gases</v>
-      </c>
-      <c r="N14" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Sistema de Gás Hospitalar</v>
       </c>
       <c r="O14" s="30" t="str">
         <f t="shared" si="8"/>
         <v>Sistema.Vacuo</v>
       </c>
-      <c r="P14" s="58" t="s">
+      <c r="P14" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q14" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T14" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U14" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Sistema.de.Gás.Hospitalar</v>
+      </c>
+      <c r="V14" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W14" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-14</v>
+      </c>
+      <c r="X14" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y14" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="Q14" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="R14" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T14" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U14" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Sistema.de.Gás.Hospitalar</v>
-      </c>
-      <c r="V14" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W14" s="66" t="str">
+      <c r="Z14" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA14" s="30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="58">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Key-GAS-14</v>
-      </c>
-      <c r="X14" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y14" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z14" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA14" s="30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="33" t="str">
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M15" s="33" t="str">
         <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M15" s="33" t="str">
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N15" s="33" t="str">
         <f t="shared" si="12"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N15" s="33" t="str">
-        <f t="shared" si="13"/>
         <v>Peças Gás</v>
       </c>
       <c r="O15" s="30" t="str">
         <f>IF(ISNUMBER(FIND("Ifc",F15)),CONCATENATE("Classe IFC:   ",F15),CONCATENATE("",F15))</f>
         <v>Queimador</v>
       </c>
-      <c r="P15" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q15" s="58" t="s">
+      <c r="P15" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q15" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="R15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T15" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U15" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V15" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W15" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-15</v>
+      </c>
+      <c r="X15" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y15" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z15" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA15" s="30" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="58">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N16" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O16" s="30" t="str">
+        <f t="shared" ref="O16:O29" si="18">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
+        <v>Registro.de.Gás</v>
+      </c>
+      <c r="P16" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q16" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="R16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T16" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U16" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V16" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W16" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-16</v>
+      </c>
+      <c r="X16" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y16" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z16" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA16" s="30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="58">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N17" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O17" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Válvula.de.Gás</v>
+      </c>
+      <c r="P17" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q17" s="52" t="s">
+        <v>150</v>
+      </c>
+      <c r="R17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T17" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U17" s="30" t="str">
+        <f t="shared" si="13"/>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V17" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W17" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-17</v>
+      </c>
+      <c r="X17" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y17" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z17" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA17" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="58">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="33" t="str">
+        <f t="shared" ref="L18" si="19">CONCATENATE("", C18)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M18" s="33" t="str">
+        <f t="shared" ref="M18" si="20">CONCATENATE("", D18)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N18" s="33" t="str">
+        <f t="shared" ref="N18" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O18" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Medidor.de.Gás</v>
+      </c>
+      <c r="P18" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q18" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="R15" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T15" s="35" t="s">
+      <c r="R18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T18" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U18" s="30" t="str">
+        <f t="shared" ref="U18" si="22">SUBSTITUTE(E18, "_", " ")</f>
+        <v>Peças.Gás</v>
+      </c>
+      <c r="V18" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U15" s="35" t="str">
-        <f t="shared" si="14"/>
+      <c r="W18" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-18</v>
+      </c>
+      <c r="X18" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y18" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z18" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA18" s="30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="58">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="33" t="str">
+        <f t="shared" si="10"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M19" s="33" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N19" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v>Peças Gás</v>
+      </c>
+      <c r="O19" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Acessório.de.Gás</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q19" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T19" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U19" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V15" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W15" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-15</v>
-      </c>
-      <c r="X15" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y15" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z15" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA15" s="30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="47" t="s">
+      <c r="V19" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W19" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-19</v>
+      </c>
+      <c r="X19" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y19" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z19" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA19" s="30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="58">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M16" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N16" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O16" s="30" t="str">
-        <f t="shared" ref="O16:O29" si="19">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
-        <v>Registro.de.Gás</v>
-      </c>
-      <c r="P16" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q16" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="R16" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T16" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U16" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V16" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W16" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-16</v>
-      </c>
-      <c r="X16" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y16" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z16" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M17" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N17" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O17" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Válvula.de.Gás</v>
-      </c>
-      <c r="P17" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q17" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="R17" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T17" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U17" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V17" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W17" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-17</v>
-      </c>
-      <c r="X17" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y17" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z17" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="33" t="str">
-        <f t="shared" ref="L18" si="20">CONCATENATE("", C18)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M18" s="33" t="str">
-        <f t="shared" ref="M18" si="21">CONCATENATE("", D18)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N18" s="33" t="str">
-        <f t="shared" ref="N18" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O18" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Medidor.de.Gás</v>
-      </c>
-      <c r="P18" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="R18" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T18" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U18" s="35" t="str">
-        <f t="shared" ref="U18" si="23">SUBSTITUTE(E18, "_", " ")</f>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V18" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W18" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-18</v>
-      </c>
-      <c r="X18" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y18" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z18" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA18" s="30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="32">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="33" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M19" s="33" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N19" s="33" t="str">
-        <f t="shared" si="13"/>
-        <v>Peças Gás</v>
-      </c>
-      <c r="O19" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Acessório.de.Gás</v>
-      </c>
-      <c r="P19" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q19" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="R19" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T19" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U19" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v>Peças.Gás</v>
-      </c>
-      <c r="V19" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W19" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-19</v>
-      </c>
-      <c r="X19" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="Y19" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z19" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA19" s="30" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="32">
-        <v>20</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="37" t="s">
+      <c r="G20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
@@ -4087,80 +4137,80 @@
         <v>Peças Gás</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Buchão.de.Gás</v>
       </c>
-      <c r="P20" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q20" s="58" t="s">
-        <v>159</v>
-      </c>
-      <c r="R20" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T20" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U20" s="35" t="str">
+      <c r="P20" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q20" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="R20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T20" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U20" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V20" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W20" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V20" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W20" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-20</v>
       </c>
       <c r="X20" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z20" s="34" t="s">
-        <v>241</v>
+        <v>113</v>
+      </c>
+      <c r="Z20" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="32">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="58">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>110</v>
+        <v>256</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K21" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
@@ -4176,80 +4226,80 @@
         <v>Peças Gás</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Cilindro.de.Gás</v>
       </c>
-      <c r="P21" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q21" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="R21" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T21" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U21" s="35" t="str">
+      <c r="P21" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q21" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="R21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T21" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U21" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V21" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W21" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V21" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W21" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-21</v>
       </c>
       <c r="X21" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z21" s="34" t="s">
-        <v>241</v>
+        <v>113</v>
+      </c>
+      <c r="Z21" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="58">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>110</v>
+        <v>256</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
@@ -4265,80 +4315,80 @@
         <v>Peças Gás</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Tanque.de.Gás</v>
       </c>
-      <c r="P22" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q22" s="58" t="s">
-        <v>235</v>
-      </c>
-      <c r="R22" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T22" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U22" s="35" t="str">
+      <c r="P22" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q22" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="R22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T22" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U22" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
-      <c r="V22" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W22" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V22" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W22" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-22</v>
       </c>
       <c r="X22" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z22" s="34" t="s">
-        <v>241</v>
+        <v>113</v>
+      </c>
+      <c r="Z22" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="32">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="58">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>110</v>
+        <v>256</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
@@ -4354,80 +4404,80 @@
         <v>Gás Doméstico</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Aquecedor.a.Gás</v>
       </c>
-      <c r="P23" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q23" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="R23" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T23" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U23" s="35" t="str">
+      <c r="P23" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q23" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="R23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T23" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U23" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V23" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W23" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V23" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W23" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z23" s="34" t="s">
-        <v>241</v>
+        <v>114</v>
+      </c>
+      <c r="Z23" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="32">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="58">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>110</v>
+        <v>256</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
@@ -4443,80 +4493,80 @@
         <v>Gás Doméstico</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Boiler.a.Gás</v>
       </c>
-      <c r="P24" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q24" s="58" t="s">
+      <c r="P24" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q24" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="R24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="R24" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T24" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U24" s="35" t="str">
+      <c r="T24" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U24" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V24" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W24" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V24" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W24" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z24" s="34" t="s">
-        <v>241</v>
+        <v>114</v>
+      </c>
+      <c r="Z24" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="58">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>110</v>
+        <v>256</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
@@ -4532,491 +4582,491 @@
         <v>Gás Doméstico</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>Caldeira.a.Gás</v>
       </c>
-      <c r="P25" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q25" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R25" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T25" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U25" s="35" t="str">
+      <c r="P25" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q25" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="R25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S25" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T25" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U25" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
-      <c r="V25" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W25" s="66" t="str">
-        <f t="shared" si="10"/>
+      <c r="V25" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W25" s="59" t="str">
+        <f t="shared" si="3"/>
         <v>Key-GAS-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z25" s="34" t="s">
-        <v>241</v>
+        <v>115</v>
+      </c>
+      <c r="Z25" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="AA25" s="30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="58">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" ref="L26" si="23">CONCATENATE("", C26)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M26" s="33" t="str">
+        <f t="shared" ref="M26" si="24">CONCATENATE("", D26)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N26" s="33" t="str">
+        <f t="shared" ref="N26" si="25">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E26),"."," ")," De "," de "))</f>
+        <v>Gás Doméstico</v>
+      </c>
+      <c r="O26" s="30" t="str">
+        <f t="shared" ref="O26" si="26">IF(ISNUMBER(FIND("Ifc",F26)),CONCATENATE("Classe IFC:   ",F26),CONCATENATE("",F26))</f>
+        <v>Tubulação.Gás</v>
+      </c>
+      <c r="P26" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q26" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T26" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U26" s="30" t="str">
+        <f t="shared" ref="U26" si="27">SUBSTITUTE(E26, "_", " ")</f>
+        <v>Gás.Doméstico</v>
+      </c>
+      <c r="V26" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W26" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-26</v>
+      </c>
+      <c r="X26" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y26" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z26" s="30" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="32">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="47" t="s">
+      <c r="AA26" s="30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="58">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" ref="L27:L29" si="28">CONCATENATE("", C27)</f>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" ref="M27:M29" si="29">CONCATENATE("", D27)</f>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N27" s="33" t="str">
+        <f t="shared" ref="N27:N29" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Aquecedor.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T27" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="U27" s="30" t="str">
+        <f t="shared" ref="U27:U29" si="31">SUBSTITUTE(E27, "_", " ")</f>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V27" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W27" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-27</v>
+      </c>
+      <c r="X27" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y27" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z27" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA27" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="58">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M28" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N28" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O28" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Boiler.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q28" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="R28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T28" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U28" s="30" t="str">
+        <f t="shared" si="31"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V28" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W28" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-28</v>
+      </c>
+      <c r="X28" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y28" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z28" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA28" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="58">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>Sistema.Predial</v>
+      </c>
+      <c r="M29" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>Elementos.Gases</v>
+      </c>
+      <c r="N29" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O29" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>Caldeira.a.Gás.Hospitalar</v>
+      </c>
+      <c r="P29" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q29" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="R29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T29" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U29" s="30" t="str">
+        <f t="shared" si="31"/>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V29" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="W29" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-29</v>
+      </c>
+      <c r="X29" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y29" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z29" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA29" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="E26" s="47" t="s">
+    </row>
+    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="58">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="42" t="s">
         <v>236</v>
       </c>
-      <c r="F26" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="33" t="str">
-        <f t="shared" ref="L26" si="24">CONCATENATE("", C26)</f>
+      <c r="F30" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="33" t="str">
+        <f t="shared" ref="L30" si="32">CONCATENATE("", C30)</f>
         <v>Sistema.Predial</v>
       </c>
-      <c r="M26" s="33" t="str">
-        <f t="shared" ref="M26" si="25">CONCATENATE("", D26)</f>
+      <c r="M30" s="33" t="str">
+        <f t="shared" ref="M30" si="33">CONCATENATE("", D30)</f>
         <v>Elementos.Gases</v>
       </c>
-      <c r="N26" s="33" t="str">
-        <f t="shared" ref="N26" si="26">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E26),"."," ")," De "," de "))</f>
-        <v>Gás Doméstico</v>
-      </c>
-      <c r="O26" s="30" t="str">
-        <f t="shared" ref="O26" si="27">IF(ISNUMBER(FIND("Ifc",F26)),CONCATENATE("Classe IFC:   ",F26),CONCATENATE("",F26))</f>
-        <v>Tubulação.Gás</v>
-      </c>
-      <c r="P26" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q26" s="58" t="s">
-        <v>155</v>
-      </c>
-      <c r="R26" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T26" s="35" t="s">
+      <c r="N30" s="33" t="str">
+        <f t="shared" ref="N30" si="34">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
+        <v>Gás Hospitalar</v>
+      </c>
+      <c r="O30" s="30" t="str">
+        <f t="shared" ref="O30" si="35">IF(ISNUMBER(FIND("Ifc",F30)),CONCATENATE("Classe IFC:   ",F30),CONCATENATE("",F30))</f>
+        <v>Tubulação.Gás.Hospitalar</v>
+      </c>
+      <c r="P30" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q30" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="T30" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" ref="U30" si="36">SUBSTITUTE(E30, "_", " ")</f>
+        <v>Gás.Hospitalar</v>
+      </c>
+      <c r="V30" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="U26" s="35" t="str">
-        <f t="shared" ref="U26" si="28">SUBSTITUTE(E26, "_", " ")</f>
-        <v>Gás.Doméstico</v>
-      </c>
-      <c r="V26" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W26" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-26</v>
-      </c>
-      <c r="X26" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y26" s="29" t="s">
+      <c r="W30" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-GAS-30</v>
+      </c>
+      <c r="X30" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="Z26" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA26" s="30" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="33" t="str">
-        <f t="shared" ref="L27:L29" si="29">CONCATENATE("", C27)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M27" s="33" t="str">
-        <f t="shared" ref="M27:M29" si="30">CONCATENATE("", D27)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N27" s="33" t="str">
-        <f t="shared" ref="N27:N29" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O27" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Aquecedor.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P27" s="58" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q27" s="58" t="s">
-        <v>210</v>
-      </c>
-      <c r="R27" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T27" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U27" s="35" t="str">
-        <f t="shared" ref="U27:U29" si="32">SUBSTITUTE(E27, "_", " ")</f>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V27" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W27" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-27</v>
-      </c>
-      <c r="X27" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y27" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z27" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA27" s="30" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L28" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M28" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N28" s="33" t="str">
-        <f t="shared" si="31"/>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O28" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Boiler.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P28" s="58" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q28" s="58" t="s">
-        <v>211</v>
-      </c>
-      <c r="R28" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T28" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U28" s="35" t="str">
-        <f t="shared" si="32"/>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V28" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W28" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-28</v>
-      </c>
-      <c r="X28" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y28" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z28" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA28" s="30" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="32">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K29" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L29" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M29" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N29" s="33" t="str">
-        <f t="shared" si="31"/>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O29" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Caldeira.a.Gás.Hospitalar</v>
-      </c>
-      <c r="P29" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q29" s="58" t="s">
-        <v>212</v>
-      </c>
-      <c r="R29" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T29" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U29" s="35" t="str">
-        <f t="shared" si="32"/>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V29" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W29" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-29</v>
-      </c>
-      <c r="X29" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y29" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z29" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA29" s="30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="33" t="str">
-        <f t="shared" ref="L30" si="33">CONCATENATE("", C30)</f>
-        <v>Sistema.Predial</v>
-      </c>
-      <c r="M30" s="33" t="str">
-        <f t="shared" ref="M30" si="34">CONCATENATE("", D30)</f>
-        <v>Elementos.Gases</v>
-      </c>
-      <c r="N30" s="33" t="str">
-        <f t="shared" ref="N30" si="35">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
-        <v>Gás Hospitalar</v>
-      </c>
-      <c r="O30" s="30" t="str">
-        <f t="shared" ref="O30" si="36">IF(ISNUMBER(FIND("Ifc",F30)),CONCATENATE("Classe IFC:   ",F30),CONCATENATE("",F30))</f>
-        <v>Tubulação.Gás.Hospitalar</v>
-      </c>
-      <c r="P30" s="58" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q30" s="58" t="s">
-        <v>209</v>
-      </c>
-      <c r="R30" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T30" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="U30" s="35" t="str">
-        <f t="shared" ref="U30" si="37">SUBSTITUTE(E30, "_", " ")</f>
-        <v>Gás.Hospitalar</v>
-      </c>
-      <c r="V30" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="W30" s="66" t="str">
-        <f t="shared" si="10"/>
-        <v>Key-GAS-30</v>
-      </c>
-      <c r="X30" s="29" t="s">
-        <v>106</v>
-      </c>
       <c r="Y30" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z30" s="34" t="s">
-        <v>243</v>
+        <v>104</v>
+      </c>
+      <c r="Z30" s="30" t="s">
+        <v>242</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -5024,36 +5074,41 @@
     <sortCondition ref="F7:F891"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A30">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
-    <cfRule type="cellIs" dxfId="19" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1484"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="13" priority="1506"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1456"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1477"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1484"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA30">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA7:AA30">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B30">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5065,15 +5120,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5138,7 +5193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5203,7 +5258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5270,7 +5325,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5286,328 +5341,327 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.85" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3046875" customWidth="1"/>
-    <col min="3" max="3" width="6.61328125" customWidth="1"/>
-    <col min="4" max="4" width="7.07421875" customWidth="1"/>
-    <col min="5" max="5" width="7.15234375" customWidth="1"/>
-    <col min="6" max="6" width="4.61328125" customWidth="1"/>
-    <col min="7" max="7" width="62.3828125" customWidth="1"/>
-    <col min="8" max="8" width="5.3046875" customWidth="1"/>
-    <col min="9" max="9" width="17.07421875" customWidth="1"/>
-    <col min="10" max="10" width="7.3828125" customWidth="1"/>
-    <col min="11" max="11" width="4.765625" customWidth="1"/>
-    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.4609375" customWidth="1"/>
-    <col min="14" max="14" width="4.921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.4609375" customWidth="1"/>
-    <col min="16" max="16" width="3.921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.3046875" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="5" width="7.140625" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="62.42578125" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.42578125" customWidth="1"/>
+    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>77</v>
-      </c>
       <c r="I1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="55" t="s">
+      <c r="J2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="55" t="s">
+      <c r="L2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="55" t="s">
+      <c r="P2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="55" t="s">
+      <c r="R2" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>100</v>
+        <v>194</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="55" t="s">
-        <v>78</v>
+        <v>197</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="J3" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="J3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="49" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="38" t="s">
+      <c r="B4" s="47" t="s">
         <v>195</v>
       </c>
+      <c r="C4" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>194</v>
+      </c>
       <c r="F4" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="H4" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="55" t="s">
-        <v>258</v>
+      <c r="J4" s="49" t="s">
+        <v>254</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="L4" s="55" t="s">
-        <v>259</v>
+        <v>106</v>
+      </c>
+      <c r="L4" s="49" t="s">
+        <v>255</v>
       </c>
       <c r="M4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="P4" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N4" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="P4" s="55" t="s">
+      <c r="Q4" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q4" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="R4" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S4" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.85" customHeight="1" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>195</v>
+      <c r="B5" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>194</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="H5" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="49" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="55" t="s">
-        <v>258</v>
+      <c r="J5" s="49" t="s">
+        <v>254</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" s="55" t="s">
-        <v>259</v>
+        <v>106</v>
+      </c>
+      <c r="L5" s="49" t="s">
+        <v>255</v>
       </c>
       <c r="M5" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="P5" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="N5" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="P5" s="55" t="s">
+      <c r="Q5" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="R5" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="Q5" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="R5" s="55" t="s">
-        <v>104</v>
-      </c>
       <c r="S5" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5617,38 +5671,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.921875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.23046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
       <c r="B1" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5677,22 +5731,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/GASE/Ontologia_Gases.xlsx
+++ b/Versão5/GASE/Ontologia_Gases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CFD370-80D6-47AF-8887-3C29090B4EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD202A30-729F-445C-8BCF-5B6C897A83E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -401,9 +401,6 @@
     <t>"Indivíduo Conteiner Superior que representa Informações contidas no Projeto Específico 01"</t>
   </si>
   <si>
-    <t>Sistema.Predial</t>
-  </si>
-  <si>
     <t>Tubulações</t>
   </si>
   <si>
@@ -842,13 +839,16 @@
     <t>quem.forneceu</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
     <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Sistemas.Prediais</t>
   </si>
 </sst>
 </file>
@@ -1381,71 +1381,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
@@ -2077,15 +2013,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2096,7 +2032,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2107,18 +2043,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2129,7 +2065,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2141,7 +2077,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2153,7 +2089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2164,7 +2100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2175,7 +2111,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2186,7 +2122,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2197,7 +2133,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2208,7 +2144,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2219,7 +2155,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2230,7 +2166,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2241,7 +2177,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2252,7 +2188,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2263,30 +2199,30 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C17" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46216.380840972219</v>
+        <v>46243.521480208336</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2297,7 +2233,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2308,7 +2244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2319,29 +2255,29 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="40" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>91</v>
       </c>
@@ -2362,35 +2298,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="62" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.53515625" style="62" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.28515625" style="55" customWidth="1"/>
-    <col min="26" max="26" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="54"/>
+    <col min="20" max="20" width="6.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.3046875" style="55" customWidth="1"/>
+    <col min="26" max="26" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>96</v>
       </c>
@@ -2473,21 +2409,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F2" s="57" t="s">
         <v>83</v>
@@ -2524,7 +2460,7 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q2" s="30" t="s">
         <v>85</v>
@@ -2545,7 +2481,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W2" s="59" t="str">
         <f t="shared" ref="W2:W30" si="3">CONCATENATE("Key-GAS-",A2)</f>
@@ -2558,31 +2494,31 @@
         <v>9</v>
       </c>
       <c r="Z2" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AA2" s="30" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2616,7 +2552,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>85</v>
@@ -2637,7 +2573,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2657,24 +2593,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -2708,7 +2644,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q4" s="30" t="s">
         <v>85</v>
@@ -2729,7 +2665,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2749,24 +2685,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -2800,7 +2736,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q5" s="30" t="s">
         <v>85</v>
@@ -2821,7 +2757,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2841,24 +2777,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -2892,7 +2828,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q6" s="30" t="s">
         <v>85</v>
@@ -2913,7 +2849,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="3"/>
@@ -2933,24 +2869,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D7" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>125</v>
-      </c>
       <c r="F7" s="42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -2969,7 +2905,7 @@
       </c>
       <c r="L7" s="33" t="str">
         <f t="shared" ref="L7:L25" si="5">CONCATENATE("", C7)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="33" t="str">
         <f t="shared" ref="M7:M25" si="6">CONCATENATE("", D7)</f>
@@ -2984,62 +2920,62 @@
         <v>Sistema.GAS</v>
       </c>
       <c r="P7" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q7" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="Q7" s="52" t="s">
-        <v>148</v>
-      </c>
       <c r="R7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T7" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U7" s="30" t="str">
         <f t="shared" ref="U7:U25" si="9">SUBSTITUTE(E7, "_", " ")</f>
         <v>Sistema.de.Gás</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-7</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA7" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
@@ -3058,7 +2994,7 @@
       </c>
       <c r="L8" s="33" t="str">
         <f t="shared" ref="L8:L19" si="10">CONCATENATE("", C8)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="33" t="str">
         <f t="shared" ref="M8:M19" si="11">CONCATENATE("", D8)</f>
@@ -3073,62 +3009,62 @@
         <v>Sistema.Oxigênio</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U8" s="30" t="str">
         <f t="shared" ref="U8:U19" si="13">SUBSTITUTE(E8, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-8</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="58">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G9" s="61" t="s">
         <v>9</v>
@@ -3147,7 +3083,7 @@
       </c>
       <c r="L9" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M9" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3162,62 +3098,62 @@
         <v>Sistema.Ar.Medicinal</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T9" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U9" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-9</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA9" s="30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="58">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3236,7 +3172,7 @@
       </c>
       <c r="L10" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3251,62 +3187,62 @@
         <v>Sistema.Ar.Comprimido</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T10" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U10" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W10" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA10" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="58">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3325,7 +3261,7 @@
       </c>
       <c r="L11" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3340,62 +3276,62 @@
         <v>Sistema.Óxido.Nitroso</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U11" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W11" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-11</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y11" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA11" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="58">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3414,7 +3350,7 @@
       </c>
       <c r="L12" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3429,62 +3365,62 @@
         <v>Sistema.Nitrogênio</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R12" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T12" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U12" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W12" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-12</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y12" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA12" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="58">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3503,7 +3439,7 @@
       </c>
       <c r="L13" s="33" t="str">
         <f t="shared" ref="L13" si="14">CONCATENATE("", C13)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="33" t="str">
         <f t="shared" ref="M13" si="15">CONCATENATE("", D13)</f>
@@ -3518,62 +3454,62 @@
         <v>Sistema.Hélio</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R13" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T13" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U13" s="30" t="str">
         <f t="shared" ref="U13" si="17">SUBSTITUTE(E13, "_", " ")</f>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W13" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-13</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y13" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="58">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -3592,7 +3528,7 @@
       </c>
       <c r="L14" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3607,62 +3543,62 @@
         <v>Sistema.Vacuo</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R14" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U14" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Sistema.de.Gás.Hospitalar</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W14" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-14</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y14" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA14" s="30" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="58">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E15" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G15" s="61" t="s">
         <v>9</v>
@@ -3681,7 +3617,7 @@
       </c>
       <c r="L15" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3696,62 +3632,62 @@
         <v>Queimador</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U15" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W15" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-15</v>
       </c>
       <c r="X15" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y15" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA15" s="30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="58">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F16" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -3770,7 +3706,7 @@
       </c>
       <c r="L16" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3785,62 +3721,62 @@
         <v>Registro.de.Gás</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R16" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T16" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U16" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W16" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-16</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="58">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -3859,7 +3795,7 @@
       </c>
       <c r="L17" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="33" t="str">
         <f t="shared" si="11"/>
@@ -3874,62 +3810,62 @@
         <v>Válvula.de.Gás</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T17" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U17" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W17" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-17</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y17" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA17" s="30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="58">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -3948,7 +3884,7 @@
       </c>
       <c r="L18" s="33" t="str">
         <f t="shared" ref="L18" si="19">CONCATENATE("", C18)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="33" t="str">
         <f t="shared" ref="M18" si="20">CONCATENATE("", D18)</f>
@@ -3963,62 +3899,62 @@
         <v>Medidor.de.Gás</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R18" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T18" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U18" s="30" t="str">
         <f t="shared" ref="U18" si="22">SUBSTITUTE(E18, "_", " ")</f>
         <v>Peças.Gás</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W18" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-18</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y18" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA18" s="30" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="58">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4037,7 +3973,7 @@
       </c>
       <c r="L19" s="33" t="str">
         <f t="shared" si="10"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
         <f t="shared" si="11"/>
@@ -4052,62 +3988,62 @@
         <v>Acessório.de.Gás</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R19" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T19" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U19" s="30" t="str">
         <f t="shared" si="13"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W19" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-19</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA19" s="30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="58">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E20" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>126</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>127</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4126,7 +4062,7 @@
       </c>
       <c r="L20" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4141,26 +4077,26 @@
         <v>Buchão.de.Gás</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T20" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U20" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W20" s="59" t="str">
         <f t="shared" si="3"/>
@@ -4170,33 +4106,33 @@
         <v>105</v>
       </c>
       <c r="Y20" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA20" s="30" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="58">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4215,7 +4151,7 @@
       </c>
       <c r="L21" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4230,26 +4166,26 @@
         <v>Cilindro.de.Gás</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T21" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U21" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W21" s="59" t="str">
         <f t="shared" si="3"/>
@@ -4259,33 +4195,33 @@
         <v>105</v>
       </c>
       <c r="Y21" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA21" s="30" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="58">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4304,7 +4240,7 @@
       </c>
       <c r="L22" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4319,26 +4255,26 @@
         <v>Tanque.de.Gás</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T22" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U22" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Peças.Gás</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W22" s="59" t="str">
         <f t="shared" si="3"/>
@@ -4348,33 +4284,33 @@
         <v>105</v>
       </c>
       <c r="Y22" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA22" s="30" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="58">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4393,7 +4329,7 @@
       </c>
       <c r="L23" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4408,62 +4344,62 @@
         <v>Aquecedor.a.Gás</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T23" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U23" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W23" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-23</v>
       </c>
       <c r="X23" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y23" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA23" s="30" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="58">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4482,7 +4418,7 @@
       </c>
       <c r="L24" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4497,62 +4433,62 @@
         <v>Boiler.a.Gás</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q24" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="R24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="S24" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="R24" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="30" t="s">
-        <v>161</v>
-      </c>
       <c r="T24" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U24" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W24" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-24</v>
       </c>
       <c r="X24" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y24" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA24" s="30" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="58">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -4571,7 +4507,7 @@
       </c>
       <c r="L25" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
         <f t="shared" si="6"/>
@@ -4586,62 +4522,62 @@
         <v>Caldeira.a.Gás</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T25" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U25" s="30" t="str">
         <f t="shared" si="9"/>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W25" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-25</v>
       </c>
       <c r="X25" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y25" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA25" s="30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="58">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4660,7 +4596,7 @@
       </c>
       <c r="L26" s="33" t="str">
         <f t="shared" ref="L26" si="23">CONCATENATE("", C26)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="33" t="str">
         <f t="shared" ref="M26" si="24">CONCATENATE("", D26)</f>
@@ -4675,26 +4611,26 @@
         <v>Tubulação.Gás</v>
       </c>
       <c r="P26" s="52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q26" s="52" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T26" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U26" s="30" t="str">
         <f t="shared" ref="U26" si="27">SUBSTITUTE(E26, "_", " ")</f>
         <v>Gás.Doméstico</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W26" s="59" t="str">
         <f t="shared" si="3"/>
@@ -4707,30 +4643,30 @@
         <v>104</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AA26" s="30" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="58">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G27" s="61" t="s">
         <v>9</v>
@@ -4749,7 +4685,7 @@
       </c>
       <c r="L27" s="33" t="str">
         <f t="shared" ref="L27:L29" si="28">CONCATENATE("", C27)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="33" t="str">
         <f t="shared" ref="M27:M29" si="29">CONCATENATE("", D27)</f>
@@ -4764,62 +4700,62 @@
         <v>Aquecedor.a.Gás.Hospitalar</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q27" s="52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T27" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U27" s="30" t="str">
         <f t="shared" ref="U27:U29" si="31">SUBSTITUTE(E27, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W27" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-27</v>
       </c>
       <c r="X27" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y27" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z27" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA27" s="30" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="58">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
@@ -4838,7 +4774,7 @@
       </c>
       <c r="L28" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="33" t="str">
         <f t="shared" si="29"/>
@@ -4853,62 +4789,62 @@
         <v>Boiler.a.Gás.Hospitalar</v>
       </c>
       <c r="P28" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q28" s="52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R28" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S28" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T28" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U28" s="30" t="str">
         <f t="shared" si="31"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W28" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-28</v>
       </c>
       <c r="X28" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y28" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="58">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
@@ -4927,7 +4863,7 @@
       </c>
       <c r="L29" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="33" t="str">
         <f t="shared" si="29"/>
@@ -4942,62 +4878,62 @@
         <v>Caldeira.a.Gás.Hospitalar</v>
       </c>
       <c r="P29" s="52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q29" s="52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R29" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T29" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U29" s="30" t="str">
         <f t="shared" si="31"/>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W29" s="59" t="str">
         <f t="shared" si="3"/>
         <v>Key-GAS-29</v>
       </c>
       <c r="X29" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y29" s="29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z29" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA29" s="30" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="58">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>109</v>
+        <v>258</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G30" s="61" t="s">
         <v>9</v>
@@ -5016,7 +4952,7 @@
       </c>
       <c r="L30" s="33" t="str">
         <f t="shared" ref="L30" si="32">CONCATENATE("", C30)</f>
-        <v>Sistema.Predial</v>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="33" t="str">
         <f t="shared" ref="M30" si="33">CONCATENATE("", D30)</f>
@@ -5031,26 +4967,26 @@
         <v>Tubulação.Gás.Hospitalar</v>
       </c>
       <c r="P30" s="52" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q30" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R30" s="30" t="s">
         <v>9</v>
       </c>
       <c r="S30" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T30" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U30" s="30" t="str">
         <f t="shared" ref="U30" si="36">SUBSTITUTE(E30, "_", " ")</f>
         <v>Gás.Hospitalar</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W30" s="59" t="str">
         <f t="shared" si="3"/>
@@ -5063,10 +4999,10 @@
         <v>104</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -5074,41 +5010,36 @@
     <sortCondition ref="F7:F891"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:B30">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:D1 F1:O1 R1:X1 Z1:AA1">
-    <cfRule type="cellIs" dxfId="26" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="1491"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1491"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576 F1 F7">
-    <cfRule type="duplicateValues" dxfId="20" priority="1513"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1513"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1463"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1463"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1484"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA30">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B30">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA30">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5120,15 +5051,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5193,7 +5124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5258,7 +5189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5325,7 +5256,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5341,29 +5272,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" customWidth="1"/>
-    <col min="4" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="62.42578125" customWidth="1"/>
-    <col min="8" max="8" width="5.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3046875" customWidth="1"/>
+    <col min="3" max="3" width="6.53515625" customWidth="1"/>
+    <col min="4" max="5" width="7.15234375" customWidth="1"/>
+    <col min="6" max="6" width="4.53515625" customWidth="1"/>
+    <col min="7" max="7" width="62.3828125" customWidth="1"/>
+    <col min="8" max="8" width="5.3046875" customWidth="1"/>
+    <col min="9" max="9" width="17.15234375" customWidth="1"/>
+    <col min="10" max="10" width="7.3828125" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" customWidth="1"/>
+    <col min="12" max="12" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.3828125" customWidth="1"/>
+    <col min="14" max="14" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.3828125" customWidth="1"/>
+    <col min="16" max="16" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -5422,7 +5353,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>1</v>
       </c>
@@ -5481,15 +5412,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
@@ -5501,13 +5432,13 @@
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -5537,30 +5468,30 @@
         <v>9</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>3</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>107</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>9</v>
@@ -5569,13 +5500,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K4" s="24" t="s">
         <v>106</v>
       </c>
       <c r="L4" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>101</v>
@@ -5584,42 +5515,42 @@
         <v>100</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R4" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="50" t="s">
         <v>107</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>9</v>
@@ -5628,13 +5559,13 @@
         <v>9</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>106</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M5" s="24" t="s">
         <v>101</v>
@@ -5643,25 +5574,25 @@
         <v>100</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P5" s="49" t="s">
         <v>102</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R5" s="49" t="s">
         <v>103</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="13" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1495"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5671,15 +5602,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5702,7 +5633,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -5731,22 +5662,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="11" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
